--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1117 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1169,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2753,1240 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1227,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,17 +1288,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1304,13 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1593,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1704,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,12 +1790,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq40，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1815,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1823,10 +1831,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1926,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2259,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2394,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2505,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2616,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2727,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2838,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2949,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3060,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,7 +3171,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3282,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3369,7 +3393,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3480,7 +3504,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3591,7 +3615,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3645,7 +3669,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3730,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3821,7 +3845,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3879,22 +3903,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3932,7 +3956,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3981,12 +4005,127 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1346,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1490,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1601,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1712,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1736,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1827,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq40，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq62，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1823,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1921,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1917,32 +1949,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1950,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1974,17 +2010,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1994,13 +2030,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2028,32 +2068,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2061,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2085,33 +2129,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2187,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq54，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2172,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2180,10 +2228,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2222,7 +2282,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2333,7 +2393,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2444,7 +2504,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2555,7 +2615,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2666,7 +2726,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2777,7 +2837,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2888,7 +2948,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2949,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2999,7 +3059,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3110,7 +3170,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3221,7 +3281,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3332,7 +3392,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3453,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3443,7 +3503,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3564,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3554,7 +3614,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3675,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3669,7 +3729,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3790,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3784,7 +3844,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3905,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3895,7 +3955,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3956,7 +4016,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4010,7 +4070,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4131,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4125,7 +4185,923 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,14 +2025,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq54，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq60，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2310,32 +2310,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2343,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,33 +2371,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2421,32 +2429,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2454,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,33 +2490,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2620,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2643,32 +2659,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2676,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2700,33 +2720,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2754,32 +2778,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2787,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2811,17 +2839,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2831,13 +2859,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2865,32 +2897,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2898,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2922,33 +2958,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2976,32 +3016,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3009,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3033,33 +3077,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3087,32 +3135,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3120,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3144,17 +3196,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3164,13 +3216,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3198,32 +3254,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3231,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3255,17 +3315,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3275,13 +3335,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3309,32 +3373,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3342,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3366,33 +3434,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3729,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3844,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4070,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4185,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4300,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4415,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4530,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4645,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4817,7 +4889,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4871,7 +4943,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4932,7 +5004,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4986,7 +5058,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5119,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5101,7 +5173,923 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3264,24 +3264,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3492,32 +3492,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3525,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3553,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3569,13 +3573,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3603,32 +3611,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3636,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,33 +3672,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3802,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3801,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4032,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4055,32 +4071,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4088,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,17 +4132,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4132,17 +4152,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4170,32 +4190,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4203,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4227,37 +4251,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4285,32 +4309,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4318,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4342,17 +4370,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4362,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4400,32 +4428,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4433,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4457,17 +4489,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4477,7 +4509,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4487,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4515,32 +4547,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4548,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4572,37 +4608,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4630,32 +4666,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4663,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4687,17 +4727,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4707,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4745,12 +4785,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4778,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4786,10 +4826,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4889,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4943,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5058,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5288,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5403,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5518,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5633,7 +5685,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5859,7 +5911,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5974,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5982,7 +6034,7 @@
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -6030,12 +6082,12 @@
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6074,22 +6126,593 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AA49" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>7/28</t>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,22 +2025,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2510,17 +2510,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5023,32 +5023,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5056,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5084,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5100,17 +5104,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5253,32 +5257,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5286,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5310,37 +5318,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5368,32 +5376,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5401,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,17 +5437,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5445,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5495,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5516,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,17 +5556,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5560,17 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5598,32 +5614,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5631,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,17 +5675,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5675,12 +5695,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5746,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5785,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5857,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5911,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6087,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6202,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6256,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6432,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6486,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6658,7 +6678,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6707,12 +6727,686 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,14 +2505,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,13 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2745,7 +2749,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2934,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,22 +2977,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3092,22 +3096,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3464,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,22 +3691,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3806,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4162,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,17 +4270,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4638,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4995,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5348,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,14 +5456,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -5467,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5624,24 +5628,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5651,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5733,32 +5737,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5766,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5790,17 +5798,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5810,13 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5844,32 +5856,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -5877,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5901,37 +5917,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5959,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5992,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,37 +6036,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6074,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6107,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,37 +6155,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6189,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6222,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6246,37 +6274,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6391,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6419,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6452,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6476,32 +6508,32 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6567,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6678,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6732,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6904,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6958,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,7 +7162,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7184,7 +7216,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,7 +7388,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7400,13 +7432,707 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,13 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4280,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,14 +4512,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -4523,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5233,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5828,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5947,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6223,24 +6227,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6250,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6332,32 +6336,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6365,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6389,17 +6397,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6409,7 +6417,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6457,24 +6465,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6484,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6541,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6566,32 +6574,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6599,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,17 +6635,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6643,13 +6655,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6677,32 +6693,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6710,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,37 +6754,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6792,12 +6812,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq25推进至seq55，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6825,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6833,10 +6853,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>沪南路华夏西路</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq21映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置白桦路明月路 ETA 11分钟参与校验</t>
+        </is>
+      </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -6903,32 +6939,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6936,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6960,17 +7000,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6980,17 +7020,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7090,7 +7130,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7162,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7277,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7388,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7442,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7557,7 +7597,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7733,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7787,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7897,12 +7937,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7963,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8078,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8127,12 +8167,468 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2276,13 +2276,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2524,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3176,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,14 +3219,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -3230,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3821,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4289,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4408,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4877,7 +4881,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5003,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6135,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6821,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq25推进至seq55，推进30站，达到≥2站确认条件</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq25推进至seq61，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6845,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6900,7 +6904,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6976,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7030,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7260,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7284,32 +7288,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7317,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7349,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7361,13 +7369,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7482,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7597,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7773,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7827,7 +7839,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7942,7 +7954,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8057,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8172,7 +8184,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8402,7 +8414,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8517,7 +8529,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8525,22 +8537,22 @@
       <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8573,12 +8585,12 @@
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8592,7 +8604,7 @@
       <c r="T69" s="2" t="inlineStr"/>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
@@ -8629,6 +8641,232 @@
       <c r="AC69" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2030,17 +2030,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7173,32 +7173,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7206,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,17 +7234,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7250,17 +7254,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7298,24 +7302,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7325,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7374,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7407,32 +7411,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7440,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7472,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7484,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7522,32 +7530,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7555,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7591,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7599,7 +7611,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7609,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7785,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7900,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7954,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8130,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8184,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8360,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8414,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8590,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8701,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8759,22 +8771,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8807,12 +8819,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8826,47 +8838,392 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
+      <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>8/28</t>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3815,17 +3815,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,14 +4754,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7649,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7682,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,17 +7710,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7726,12 +7730,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7764,32 +7768,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7797,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,17 +7829,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7841,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7887,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7912,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,17 +7948,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7956,17 +7968,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7994,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8027,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8067,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8071,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8224,32 +8240,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8257,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,17 +8301,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8301,17 +8321,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8426,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8541,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8713,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8824,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8939,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9054,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9169,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9223,7 +9243,812 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC81"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>126.3</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1915,13 +1915,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,14 +2029,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2286,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2355,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2390,7 +2394,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2524,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,7 +2628,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2639,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3353,7 +3357,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>27/28</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3537,7 +3541,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3710,7 +3714,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,7 +3929,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3935,12 +3939,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,12 +4287,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4358,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,14 +4401,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>126.3</t>
@@ -4412,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,22 +4520,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,17 +4644,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4953,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4997,17 +5001,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5241,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,14 +5349,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -5360,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,7 +5587,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5663,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5717,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,7 +5825,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5836,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5959,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6496,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,12 +6544,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6615,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6734,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,17 +6782,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6980,7 +6984,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7019,14 +7023,14 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>126.3</t>
@@ -7034,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7139,13 +7143,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,14 +7257,14 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -7264,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,7 +7495,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7502,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -8125,32 +8133,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8158,7 +8170,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,17 +8194,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8202,12 +8214,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8250,24 +8262,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8277,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8316,7 +8328,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8326,12 +8338,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8359,32 +8371,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8392,7 +8408,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,17 +8432,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8436,17 +8452,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8474,32 +8490,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8507,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8531,37 +8551,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8609,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8622,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8630,10 +8650,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr"/>
-      <c r="S69" s="2" t="inlineStr"/>
-      <c r="T69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -8700,32 +8736,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8733,7 +8773,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8757,17 +8797,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8777,13 +8817,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -8811,32 +8855,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8844,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,17 +8916,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8888,17 +8936,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -8959,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9074,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9189,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9243,7 +9291,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9358,7 +9406,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9473,7 +9521,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9649,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9764,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9818,7 +9866,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9994,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10052,6 +10100,696 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>121.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>126.3</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2513,14 +2513,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3104,14 +3104,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>123.3</t>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3466,17 +3466,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3580,22 +3580,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4168,17 +4168,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,14 +5468,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>123.3</t>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6425,17 +6425,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7381,17 +7381,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7614,14 +7614,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7733,14 +7733,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>123.3</t>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8746,24 +8746,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8865,24 +8865,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -8974,32 +8974,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9007,7 +9011,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9031,27 +9035,27 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -9089,32 +9093,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9122,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9146,37 +9154,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -9204,32 +9212,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9237,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9261,27 +9273,27 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9291,7 +9303,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -9319,32 +9331,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9352,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9376,17 +9392,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9396,17 +9412,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9434,32 +9450,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9467,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,17 +9511,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9511,12 +9531,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9549,32 +9569,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9582,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,17 +9630,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9626,17 +9650,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -9664,32 +9688,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9697,7 +9725,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,17 +9749,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9741,17 +9769,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9866,7 +9894,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9955,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10042,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10096,7 +10124,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10272,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10326,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10441,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10617,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10732,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10790,6 +10818,922 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>123.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>121.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3461,22 +3461,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,22 +4044,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,22 +4163,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4758,22 +4758,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>121.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,17 +5706,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,22 +6420,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6658,22 +6658,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9460,24 +9460,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9526,17 +9526,17 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9579,24 +9579,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9645,22 +9645,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -9688,36 +9688,32 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9725,7 +9721,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9749,37 +9745,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -9807,32 +9803,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9864,37 +9864,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -9922,32 +9922,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9955,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9979,37 +9983,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -10037,32 +10041,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10070,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10094,17 +10102,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10114,17 +10122,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -10152,32 +10160,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10185,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10209,17 +10221,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10229,12 +10241,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>121.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10267,32 +10279,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10300,7 +10316,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10324,17 +10340,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10344,12 +10360,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10415,7 +10431,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10469,7 +10485,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10546,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10645,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10760,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10875,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10990,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11101,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11155,7 +11171,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11331,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11385,7 +11401,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11462,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11500,7 +11516,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -11508,7 +11524,7 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -11556,12 +11572,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11610,12 +11626,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -11623,22 +11639,22 @@
       <c r="A95" s="2" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -11671,12 +11687,12 @@
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11690,47 +11706,852 @@
       <c r="T95" s="2" t="inlineStr"/>
       <c r="U95" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z95" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
         <is>
           <t>123.0</t>
         </is>
       </c>
-      <c r="AC95" s="2" t="inlineStr">
+      <c r="AC96" s="2" t="inlineStr">
         <is>
           <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>133.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>26/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC102"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2034,17 +2034,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2518,17 +2518,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3228,17 +3228,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3934,17 +3934,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4525,17 +4525,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5354,17 +5354,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5473,17 +5473,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7262,17 +7262,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7500,17 +7500,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7619,17 +7619,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8571,17 +8571,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -10398,32 +10398,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10431,7 +10435,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10455,17 +10459,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10475,17 +10479,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10517,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10546,7 +10554,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10570,17 +10578,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10590,17 +10598,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -10628,32 +10636,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10661,7 +10673,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10685,17 +10697,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10705,17 +10717,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -10743,32 +10755,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10776,7 +10792,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10800,17 +10816,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10820,17 +10836,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -10945,7 +10961,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -10973,12 +10989,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq63，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -11006,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11014,10 +11030,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q89" s="2" t="inlineStr"/>
-      <c r="R89" s="2" t="inlineStr"/>
-      <c r="S89" s="2" t="inlineStr"/>
-      <c r="T89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11084,32 +11116,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11117,7 +11153,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11141,17 +11177,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11161,17 +11197,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -11199,32 +11235,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11232,7 +11272,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11256,17 +11296,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11276,12 +11316,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11347,7 +11387,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11429,32 +11469,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11462,7 +11506,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11486,17 +11530,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11506,17 +11550,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -11544,12 +11588,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -11577,7 +11621,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11585,10 +11629,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
-      <c r="S94" s="2" t="inlineStr"/>
-      <c r="T94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11692,7 +11752,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11746,7 +11806,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11867,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11922,7 +11982,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12037,7 +12097,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12152,7 +12212,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12267,7 +12327,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12382,7 +12442,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12497,7 +12557,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12551,7 +12611,237 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>126.7</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>121.7</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3585,17 +3585,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8936,17 +8936,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9060,12 +9060,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9174,17 +9174,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -11354,32 +11354,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11387,7 +11391,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11411,17 +11415,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11431,17 +11435,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -11479,24 +11483,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11506,7 +11510,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11555,12 +11559,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11597,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -11621,7 +11625,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11719,32 +11723,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11752,7 +11760,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11776,17 +11784,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11796,17 +11804,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -11834,32 +11842,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11867,7 +11879,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11891,17 +11903,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11911,17 +11923,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11994,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12036,7 +12048,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -12064,12 +12076,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq41，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12097,7 +12109,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12105,10 +12117,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:44</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置迎春路金松路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12212,7 +12240,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12327,7 +12355,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12442,7 +12470,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12496,7 +12524,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -12557,7 +12585,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12672,7 +12700,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12787,7 +12815,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12841,7 +12869,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11864,12 +11864,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq41，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq52，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12207,32 +12207,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12240,7 +12244,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12264,17 +12268,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12284,12 +12288,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12355,7 +12359,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12470,7 +12474,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12585,7 +12589,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12700,7 +12704,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12815,7 +12819,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">

--- a/data/export/2026-10-04-浦东35路.xlsx
+++ b/data/export/2026-10-04-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4168,17 +4168,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4763,17 +4763,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5949,17 +5949,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7857,17 +7857,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9650,17 +9650,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9884,17 +9884,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq52，推进19站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq33推进至seq62，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12326,32 +12326,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12359,7 +12363,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12383,17 +12387,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12403,17 +12407,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -12441,32 +12445,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12474,7 +12482,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12498,17 +12506,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12518,17 +12526,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -12556,32 +12564,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12589,7 +12601,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12613,17 +12625,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12633,17 +12645,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -12671,32 +12683,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12704,7 +12720,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12728,17 +12744,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12748,17 +12764,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12835,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
